--- a/04_Figures/F2/c_data/F2.xlsx
+++ b/04_Figures/F2/c_data/F2.xlsx
@@ -769,7 +769,7 @@
     <t>02_HRvLR/01_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>e893235f4b5f4bcc6d90e734d17538c3</t>
+    <t>13a22822b5138c9cba237b44f432c400</t>
   </si>
   <si>
     <t>corrected</t>

--- a/04_Figures/F2/c_data/F2.xlsx
+++ b/04_Figures/F2/c_data/F2.xlsx
@@ -769,7 +769,7 @@
     <t>02_HRvLR/01_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>13a22822b5138c9cba237b44f432c400</t>
+    <t>e706deccf806204996a968b97f852521</t>
   </si>
   <si>
     <t>corrected</t>

--- a/04_Figures/F2/c_data/F2.xlsx
+++ b/04_Figures/F2/c_data/F2.xlsx
@@ -392,7 +392,7 @@
     <t>02_HRvLR/01_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>eb23e8a1866fdf41427417935863def8</t>
+    <t>f1b9b3d5ee159b256de22fc2b72e89ce</t>
   </si>
   <si>
     <t>BiocManager</t>

--- a/04_Figures/F2/c_data/F2.xlsx
+++ b/04_Figures/F2/c_data/F2.xlsx
@@ -7,167 +7,52 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="read_me" sheetId="1" r:id="rId1"/>
-    <sheet name="columns" sheetId="2" r:id="rId2"/>
-    <sheet name="a_responders" sheetId="3" r:id="rId3"/>
-    <sheet name="input_manifest" sheetId="4" r:id="rId4"/>
-    <sheet name="package_versions" sheetId="5" r:id="rId5"/>
+    <sheet name="a_responders" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="224">
-  <si>
-    <t>sheet</t>
-  </si>
-  <si>
-    <t>holds</t>
-  </si>
-  <si>
-    <t>columns</t>
-  </si>
-  <si>
-    <t>Every column of every sheet below, with what it holds.</t>
-  </si>
-  <si>
-    <t>a_responders</t>
-  </si>
-  <si>
-    <t>Panel a: per protein and contrast, the responders drawn (Π &lt; 0.05 in a group's training or acute contrast; top 10 per block by p) with biopsies observed, logFC, 95% CI, p, FDR and Π in every contrast.</t>
-  </si>
-  <si>
-    <t>input_manifest</t>
-  </si>
-  <si>
-    <t>Files read, with md5.</t>
-  </si>
-  <si>
-    <t>package_versions</t>
-  </si>
-  <si>
-    <t>Packages loaded at run time.</t>
-  </si>
-  <si>
-    <t>column</t>
-  </si>
-  <si>
-    <t>meaning</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="85">
   <si>
     <t>block</t>
-  </si>
-  <si>
-    <t>Row block: Shared (Π &lt; 0.05 in both groups' training or acute contrasts), HR only or LR only.</t>
   </si>
   <si>
     <t>row_order</t>
   </si>
   <si>
-    <t>Position of the protein within its block (1 at the top).</t>
-  </si>
-  <si>
     <t>uniprot_id</t>
-  </si>
-  <si>
-    <t>UniProt accession of the protein.</t>
   </si>
   <si>
     <t>gene</t>
   </si>
   <si>
-    <t>Gene symbol of the protein.</t>
-  </si>
-  <si>
     <t>n_observed</t>
-  </si>
-  <si>
-    <t>Biopsies (of 48) in which the protein had at least one observed precursor.</t>
   </si>
   <si>
     <t>contrast</t>
   </si>
   <si>
-    <t>Comparison from the design: Training_HR/LR (T2 - T1), Acute_HR/LR (T3 - T2), Baseline/Trained/Acute_HRvLR (HR - LR at T1, T2, T3), Training_Interaction and Acute_Interaction (HR's change minus LR's).</t>
-  </si>
-  <si>
     <t>logFC</t>
-  </si>
-  <si>
-    <t>Difference in log2 abundance for the contrast; positive = higher at the later time point or in HR.</t>
   </si>
   <si>
     <t>logFC_lower</t>
   </si>
   <si>
-    <t>Lower bound of the 95% confidence interval of logFC (limma topTable).</t>
-  </si>
-  <si>
     <t>logFC_upper</t>
-  </si>
-  <si>
-    <t>Upper bound of the 95% confidence interval of logFC (limma topTable).</t>
   </si>
   <si>
     <t>p</t>
   </si>
   <si>
-    <t>Nominal p-value of the row's test.</t>
-  </si>
-  <si>
     <t>fdr</t>
-  </si>
-  <si>
-    <t>Benjamini-Hochberg adjusted p-value; the sheet's read_me says within which family.</t>
   </si>
   <si>
     <t>pi_score</t>
   </si>
   <si>
-    <t>Π = p^|logFC| (Xiao et al. 2014).</t>
-  </si>
-  <si>
     <t>selection_p</t>
-  </si>
-  <si>
-    <t>p the row was ranked on: the group's smallest p over its training and acute contrasts with Π &lt; 0.05; for Shared, the larger of the two groups' values.</t>
-  </si>
-  <si>
-    <t>input</t>
-  </si>
-  <si>
-    <t>Name the script gives the file it read.</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>Path of the file read.</t>
-  </si>
-  <si>
-    <t>md5</t>
-  </si>
-  <si>
-    <t>MD5 checksum of the file read.</t>
-  </si>
-  <si>
-    <t>package</t>
-  </si>
-  <si>
-    <t>R package.</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>Package version.</t>
-  </si>
-  <si>
-    <t>source</t>
-  </si>
-  <si>
-    <t>Where the package came from.</t>
   </si>
   <si>
     <t>Shared</t>
@@ -384,312 +269,6 @@
   </si>
   <si>
     <t>HSPE1</t>
-  </si>
-  <si>
-    <t>contrasts</t>
-  </si>
-  <si>
-    <t>02_HRvLR/01_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
-  </si>
-  <si>
-    <t>f1b9b3d5ee159b256de22fc2b72e89ce</t>
-  </si>
-  <si>
-    <t>BiocManager</t>
-  </si>
-  <si>
-    <t>1.30.27</t>
-  </si>
-  <si>
-    <t>CRAN (R 4.6.0)</t>
-  </si>
-  <si>
-    <t>bit</t>
-  </si>
-  <si>
-    <t>4.6.0</t>
-  </si>
-  <si>
-    <t>bit64</t>
-  </si>
-  <si>
-    <t>4.8.0</t>
-  </si>
-  <si>
-    <t>cellranger</t>
-  </si>
-  <si>
-    <t>1.1.0</t>
-  </si>
-  <si>
-    <t>cli</t>
-  </si>
-  <si>
-    <t>3.6.6</t>
-  </si>
-  <si>
-    <t>commonmark</t>
-  </si>
-  <si>
-    <t>2.0.0</t>
-  </si>
-  <si>
-    <t>crayon</t>
-  </si>
-  <si>
-    <t>1.5.3</t>
-  </si>
-  <si>
-    <t>dplyr</t>
-  </si>
-  <si>
-    <t>1.2.1</t>
-  </si>
-  <si>
-    <t>farver</t>
-  </si>
-  <si>
-    <t>2.1.2</t>
-  </si>
-  <si>
-    <t>generics</t>
-  </si>
-  <si>
-    <t>0.1.4</t>
-  </si>
-  <si>
-    <t>ggh4x</t>
-  </si>
-  <si>
-    <t>0.3.1</t>
-  </si>
-  <si>
-    <t>ggplot2</t>
-  </si>
-  <si>
-    <t>4.0.3</t>
-  </si>
-  <si>
-    <t>ggtext</t>
-  </si>
-  <si>
-    <t>0.2.0</t>
-  </si>
-  <si>
-    <t>CRAN (R 4.6.1)</t>
-  </si>
-  <si>
-    <t>glue</t>
-  </si>
-  <si>
-    <t>1.8.1</t>
-  </si>
-  <si>
-    <t>gridtext</t>
-  </si>
-  <si>
-    <t>0.1.6</t>
-  </si>
-  <si>
-    <t>gtable</t>
-  </si>
-  <si>
-    <t>0.3.6</t>
-  </si>
-  <si>
-    <t>here</t>
-  </si>
-  <si>
-    <t>1.0.2</t>
-  </si>
-  <si>
-    <t>hms</t>
-  </si>
-  <si>
-    <t>1.1.4</t>
-  </si>
-  <si>
-    <t>labeling</t>
-  </si>
-  <si>
-    <t>0.4.3</t>
-  </si>
-  <si>
-    <t>lifecycle</t>
-  </si>
-  <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
-    <t>litedown</t>
-  </si>
-  <si>
-    <t>0.11</t>
-  </si>
-  <si>
-    <t>magrittr</t>
-  </si>
-  <si>
-    <t>2.0.5</t>
-  </si>
-  <si>
-    <t>markdown</t>
-  </si>
-  <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>pillar</t>
-  </si>
-  <si>
-    <t>1.11.1</t>
-  </si>
-  <si>
-    <t>pkgconfig</t>
-  </si>
-  <si>
-    <t>2.0.3</t>
-  </si>
-  <si>
-    <t>purrr</t>
-  </si>
-  <si>
-    <t>1.2.2</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>2.6.1</t>
-  </si>
-  <si>
-    <t>RColorBrewer</t>
-  </si>
-  <si>
-    <t>1.1-3</t>
-  </si>
-  <si>
-    <t>Rcpp</t>
-  </si>
-  <si>
-    <t>1.1.1-1.1</t>
-  </si>
-  <si>
-    <t>readr</t>
-  </si>
-  <si>
-    <t>2.2.0</t>
-  </si>
-  <si>
-    <t>readxl</t>
-  </si>
-  <si>
-    <t>1.4.5</t>
-  </si>
-  <si>
-    <t>renv</t>
-  </si>
-  <si>
-    <t>1.2.3</t>
-  </si>
-  <si>
-    <t>rlang</t>
-  </si>
-  <si>
-    <t>1.3.0</t>
-  </si>
-  <si>
-    <t>rprojroot</t>
-  </si>
-  <si>
-    <t>2.1.1</t>
-  </si>
-  <si>
-    <t>S7</t>
-  </si>
-  <si>
-    <t>0.2.2</t>
-  </si>
-  <si>
-    <t>scales</t>
-  </si>
-  <si>
-    <t>1.4.0</t>
-  </si>
-  <si>
-    <t>sessioninfo</t>
-  </si>
-  <si>
-    <t>1.2.4</t>
-  </si>
-  <si>
-    <t>stringi</t>
-  </si>
-  <si>
-    <t>1.8.7</t>
-  </si>
-  <si>
-    <t>stringr</t>
-  </si>
-  <si>
-    <t>1.6.0</t>
-  </si>
-  <si>
-    <t>tibble</t>
-  </si>
-  <si>
-    <t>3.3.1</t>
-  </si>
-  <si>
-    <t>tidyr</t>
-  </si>
-  <si>
-    <t>1.3.2</t>
-  </si>
-  <si>
-    <t>tidyselect</t>
-  </si>
-  <si>
-    <t>tzdb</t>
-  </si>
-  <si>
-    <t>0.5.0</t>
-  </si>
-  <si>
-    <t>vctrs</t>
-  </si>
-  <si>
-    <t>0.7.3</t>
-  </si>
-  <si>
-    <t>vroom</t>
-  </si>
-  <si>
-    <t>1.7.1</t>
-  </si>
-  <si>
-    <t>withr</t>
-  </si>
-  <si>
-    <t>3.0.2</t>
-  </si>
-  <si>
-    <t>xfun</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>xml2</t>
-  </si>
-  <si>
-    <t>1.5.2</t>
-  </si>
-  <si>
-    <t>yaml</t>
-  </si>
-  <si>
-    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -1032,348 +611,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E2">
         <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G2">
         <v>-0.3778086688998421</v>
@@ -1399,22 +698,22 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G3">
         <v>1.071050818354829</v>
@@ -1440,22 +739,22 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G4">
         <v>4.292435730149458</v>
@@ -1481,22 +780,22 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E5">
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G5">
         <v>4.067962396243519</v>
@@ -1522,22 +821,22 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E6">
         <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G6">
         <v>0.3129422679635887</v>
@@ -1563,22 +862,22 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E7">
         <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G7">
         <v>-1.135917219291082</v>
@@ -1604,22 +903,22 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G8">
         <v>-0.9114438853851432</v>
@@ -1645,22 +944,22 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E9">
         <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G9">
         <v>-1.448859487254671</v>
@@ -1686,22 +985,22 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E10">
         <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G10">
         <v>0.2244733339059373</v>
@@ -1727,22 +1026,22 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="E11">
         <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G11">
         <v>0.3258176057307178</v>
@@ -1768,22 +1067,22 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="E12">
         <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G12">
         <v>0.5560943190648313</v>
@@ -1809,22 +1108,22 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="E13">
         <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G13">
         <v>3.105595615846973</v>
@@ -1850,22 +1149,22 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="E14">
         <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G14">
         <v>3.866428282885021</v>
@@ -1891,22 +1190,22 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="E15">
         <v>15</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G15">
         <v>0.1861256962718194</v>
@@ -1932,22 +1231,22 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="E16">
         <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G16">
         <v>-0.04415101706229407</v>
@@ -1973,22 +1272,22 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="E17">
         <v>15</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G17">
         <v>-0.8049836841003426</v>
@@ -2014,22 +1313,22 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="E18">
         <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G18">
         <v>-0.2302767133341135</v>
@@ -2055,22 +1354,22 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="E19">
         <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G19">
         <v>-0.7608326670380485</v>
@@ -2096,22 +1395,22 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E20">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G20">
         <v>0.8491007608721794</v>
@@ -2137,22 +1436,22 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B21">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E21">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G21">
         <v>1.002025660358203</v>
@@ -2178,22 +1477,22 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E22">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G22">
         <v>-0.6887570863962615</v>
@@ -2219,22 +1518,22 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B23">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E23">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G23">
         <v>-0.9970179376811874</v>
@@ -2260,22 +1559,22 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E24">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G24">
         <v>0.01409957047174437</v>
@@ -2301,22 +1600,22 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B25">
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E25">
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G25">
         <v>-0.1388253290142796</v>
@@ -2342,22 +1641,22 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B26">
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E26">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G26">
         <v>0.1694355222706463</v>
@@ -2383,22 +1682,22 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B27">
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E27">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G27">
         <v>-0.1529248994860239</v>
@@ -2424,22 +1723,22 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B28">
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E28">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G28">
         <v>0.3082608512849259</v>
@@ -2465,22 +1764,22 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B29">
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="E29">
         <v>36</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G29">
         <v>0.5674171546545246</v>
@@ -2506,22 +1805,22 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="E30">
         <v>36</v>
       </c>
       <c r="F30" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G30">
         <v>0.5964992631969874</v>
@@ -2547,22 +1846,22 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B31">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="E31">
         <v>36</v>
       </c>
       <c r="F31" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G31">
         <v>-0.2961910472884597</v>
@@ -2588,22 +1887,22 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B32">
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="E32">
         <v>36</v>
       </c>
       <c r="F32" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G32">
         <v>-0.3526298458902311</v>
@@ -2629,22 +1928,22 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B33">
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="E33">
         <v>36</v>
       </c>
       <c r="F33" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G33">
         <v>-0.2728235301196662</v>
@@ -2670,22 +1969,22 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B34">
         <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D34" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="E34">
         <v>36</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G34">
         <v>-0.301905638662129</v>
@@ -2711,22 +2010,22 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="E35">
         <v>36</v>
       </c>
       <c r="F35" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G35">
         <v>-0.2454668400603577</v>
@@ -2752,22 +2051,22 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B36">
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D36" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="E36">
         <v>36</v>
       </c>
       <c r="F36" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G36">
         <v>-0.02908210854246285</v>
@@ -2793,22 +2092,22 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B37">
         <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D37" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="E37">
         <v>36</v>
       </c>
       <c r="F37" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G37">
         <v>0.05643879860177137</v>
@@ -2834,22 +2133,22 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B38">
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D38" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="E38">
         <v>35</v>
       </c>
       <c r="F38" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G38">
         <v>-0.3186545779833807</v>
@@ -2875,22 +2174,22 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B39">
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D39" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="E39">
         <v>35</v>
       </c>
       <c r="F39" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G39">
         <v>-0.1908265018232065</v>
@@ -2916,22 +2215,22 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B40">
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D40" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="E40">
         <v>35</v>
       </c>
       <c r="F40" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G40">
         <v>1.444232202681011</v>
@@ -2957,22 +2256,22 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B41">
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D41" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="E41">
         <v>35</v>
       </c>
       <c r="F41" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G41">
         <v>1.43350517013706</v>
@@ -2998,22 +2297,22 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B42">
         <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D42" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="E42">
         <v>35</v>
       </c>
       <c r="F42" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G42">
         <v>0.02902684120203247</v>
@@ -3039,22 +2338,22 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B43">
         <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D43" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="E43">
         <v>35</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G43">
         <v>-0.09880123495814175</v>
@@ -3080,22 +2379,22 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B44">
         <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D44" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="E44">
         <v>35</v>
       </c>
       <c r="F44" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G44">
         <v>-0.08807420241419095</v>
@@ -3121,22 +2420,22 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B45">
         <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D45" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="E45">
         <v>35</v>
       </c>
       <c r="F45" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G45">
         <v>-0.1278280761601742</v>
@@ -3162,22 +2461,22 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B46">
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="E46">
         <v>35</v>
       </c>
       <c r="F46" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G46">
         <v>0.0107270325439508</v>
@@ -3203,22 +2502,22 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B47">
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="D47" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="E47">
         <v>30</v>
       </c>
       <c r="F47" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G47">
         <v>0.7608596549843476</v>
@@ -3244,22 +2543,22 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B48">
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="D48" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="E48">
         <v>30</v>
       </c>
       <c r="F48" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G48">
         <v>0.6738878447578251</v>
@@ -3285,22 +2584,22 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B49">
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="D49" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="E49">
         <v>30</v>
       </c>
       <c r="F49" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G49">
         <v>-0.4678031362733002</v>
@@ -3326,22 +2625,22 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B50">
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="D50" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="E50">
         <v>30</v>
       </c>
       <c r="F50" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G50">
         <v>-0.4150327470002821</v>
@@ -3367,22 +2666,22 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B51">
         <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="D51" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="E51">
         <v>30</v>
       </c>
       <c r="F51" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G51">
         <v>-0.2533972650740317</v>
@@ -3408,22 +2707,22 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B52">
         <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="D52" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="E52">
         <v>30</v>
       </c>
       <c r="F52" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G52">
         <v>-0.1664254548475093</v>
@@ -3449,22 +2748,22 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B53">
         <v>6</v>
       </c>
       <c r="C53" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="D53" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="E53">
         <v>30</v>
       </c>
       <c r="F53" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G53">
         <v>-0.2191958441205273</v>
@@ -3490,22 +2789,22 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B54">
         <v>6</v>
       </c>
       <c r="C54" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="D54" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="E54">
         <v>30</v>
       </c>
       <c r="F54" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G54">
         <v>0.08697181022652245</v>
@@ -3531,22 +2830,22 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B55">
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="D55" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="E55">
         <v>30</v>
       </c>
       <c r="F55" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G55">
         <v>-0.05277038927301803</v>
@@ -3572,22 +2871,22 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B56">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D56" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="E56">
         <v>35</v>
       </c>
       <c r="F56" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G56">
         <v>0.6580880389470245</v>
@@ -3613,22 +2912,22 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B57">
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D57" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="E57">
         <v>35</v>
       </c>
       <c r="F57" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G57">
         <v>0.5423083102194362</v>
@@ -3654,22 +2953,22 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B58">
         <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D58" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="E58">
         <v>35</v>
       </c>
       <c r="F58" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G58">
         <v>-0.3579254175278415</v>
@@ -3695,22 +2994,22 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B59">
         <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D59" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="E59">
         <v>35</v>
       </c>
       <c r="F59" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G59">
         <v>-0.68715561837063</v>
@@ -3736,22 +3035,22 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B60">
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="E60">
         <v>35</v>
       </c>
       <c r="F60" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G60">
         <v>-0.6044609033608381</v>
@@ -3777,22 +3076,22 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B61">
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D61" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="E61">
         <v>35</v>
       </c>
       <c r="F61" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G61">
         <v>-0.4886811746332498</v>
@@ -3818,22 +3117,22 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B62">
         <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D62" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="E62">
         <v>35</v>
       </c>
       <c r="F62" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G62">
         <v>-0.1594509737904612</v>
@@ -3859,22 +3158,22 @@
     </row>
     <row r="63" spans="1:13">
       <c r="A63" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B63">
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D63" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="E63">
         <v>35</v>
       </c>
       <c r="F63" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G63">
         <v>0.1157797287275883</v>
@@ -3900,22 +3199,22 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B64">
         <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D64" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="E64">
         <v>35</v>
       </c>
       <c r="F64" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G64">
         <v>0.3292302008427885</v>
@@ -3941,22 +3240,22 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B65">
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D65" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="E65">
         <v>43</v>
       </c>
       <c r="F65" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G65">
         <v>-0.4443624924638137</v>
@@ -3982,22 +3281,22 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B66">
         <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D66" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="E66">
         <v>43</v>
       </c>
       <c r="F66" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G66">
         <v>0.9444205636880376</v>
@@ -4023,22 +3322,22 @@
     </row>
     <row r="67" spans="1:13">
       <c r="A67" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B67">
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D67" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="E67">
         <v>43</v>
       </c>
       <c r="F67" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G67">
         <v>0.9350696113687675</v>
@@ -4064,22 +3363,22 @@
     </row>
     <row r="68" spans="1:13">
       <c r="A68" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B68">
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D68" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="E68">
         <v>43</v>
       </c>
       <c r="F68" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G68">
         <v>-0.6281037973055454</v>
@@ -4105,22 +3404,22 @@
     </row>
     <row r="69" spans="1:13">
       <c r="A69" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B69">
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D69" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="E69">
         <v>43</v>
       </c>
       <c r="F69" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G69">
         <v>0.6736958541743867</v>
@@ -4146,22 +3445,22 @@
     </row>
     <row r="70" spans="1:13">
       <c r="A70" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B70">
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D70" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="E70">
         <v>43</v>
       </c>
       <c r="F70" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G70">
         <v>-0.7150872019774646</v>
@@ -4187,22 +3486,22 @@
     </row>
     <row r="71" spans="1:13">
       <c r="A71" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B71">
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D71" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="E71">
         <v>43</v>
       </c>
       <c r="F71" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G71">
         <v>0.8480862066968484</v>
@@ -4228,22 +3527,22 @@
     </row>
     <row r="72" spans="1:13">
       <c r="A72" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B72">
         <v>8</v>
       </c>
       <c r="C72" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D72" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="E72">
         <v>43</v>
       </c>
       <c r="F72" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G72">
         <v>-1.388783056151851</v>
@@ -4269,22 +3568,22 @@
     </row>
     <row r="73" spans="1:13">
       <c r="A73" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B73">
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D73" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="E73">
         <v>43</v>
       </c>
       <c r="F73" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G73">
         <v>1.563173408674313</v>
@@ -4310,22 +3609,22 @@
     </row>
     <row r="74" spans="1:13">
       <c r="A74" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B74">
         <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D74" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E74">
         <v>48</v>
       </c>
       <c r="F74" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G74">
         <v>0.1104799854166814</v>
@@ -4351,22 +3650,22 @@
     </row>
     <row r="75" spans="1:13">
       <c r="A75" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B75">
         <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D75" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E75">
         <v>48</v>
       </c>
       <c r="F75" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G75">
         <v>-0.1851711582227935</v>
@@ -4392,22 +3691,22 @@
     </row>
     <row r="76" spans="1:13">
       <c r="A76" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B76">
         <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D76" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E76">
         <v>48</v>
       </c>
       <c r="F76" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G76">
         <v>0.8542791562556324</v>
@@ -4433,22 +3732,22 @@
     </row>
     <row r="77" spans="1:13">
       <c r="A77" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B77">
         <v>9</v>
       </c>
       <c r="C77" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D77" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E77">
         <v>48</v>
       </c>
       <c r="F77" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G77">
         <v>0.9484858394549676</v>
@@ -4474,22 +3773,22 @@
     </row>
     <row r="78" spans="1:13">
       <c r="A78" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B78">
         <v>9</v>
       </c>
       <c r="C78" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D78" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E78">
         <v>48</v>
       </c>
       <c r="F78" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G78">
         <v>-0.2789814432471154</v>
@@ -4515,22 +3814,22 @@
     </row>
     <row r="79" spans="1:13">
       <c r="A79" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B79">
         <v>9</v>
       </c>
       <c r="C79" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D79" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E79">
         <v>48</v>
       </c>
       <c r="F79" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G79">
         <v>0.01666970039235949</v>
@@ -4556,22 +3855,22 @@
     </row>
     <row r="80" spans="1:13">
       <c r="A80" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B80">
         <v>9</v>
       </c>
       <c r="C80" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D80" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E80">
         <v>48</v>
       </c>
       <c r="F80" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G80">
         <v>-0.07753698280697563</v>
@@ -4597,22 +3896,22 @@
     </row>
     <row r="81" spans="1:13">
       <c r="A81" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B81">
         <v>9</v>
       </c>
       <c r="C81" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D81" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E81">
         <v>48</v>
       </c>
       <c r="F81" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G81">
         <v>0.2956511436394749</v>
@@ -4638,22 +3937,22 @@
     </row>
     <row r="82" spans="1:13">
       <c r="A82" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B82">
         <v>9</v>
       </c>
       <c r="C82" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="D82" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E82">
         <v>48</v>
       </c>
       <c r="F82" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G82">
         <v>-0.09420668319933512</v>
@@ -4679,22 +3978,22 @@
     </row>
     <row r="83" spans="1:13">
       <c r="A83" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B83">
         <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="D83" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="E83">
         <v>8</v>
       </c>
       <c r="F83" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G83">
         <v>-0.1105158217656541</v>
@@ -4720,22 +4019,22 @@
     </row>
     <row r="84" spans="1:13">
       <c r="A84" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B84">
         <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="D84" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="E84">
         <v>8</v>
       </c>
       <c r="F84" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G84">
         <v>0.5023720948676598</v>
@@ -4761,22 +4060,22 @@
     </row>
     <row r="85" spans="1:13">
       <c r="A85" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B85">
         <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="D85" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="E85">
         <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G85">
         <v>3.409639182609462</v>
@@ -4802,22 +4101,22 @@
     </row>
     <row r="86" spans="1:13">
       <c r="A86" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B86">
         <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="D86" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="E86">
         <v>8</v>
       </c>
       <c r="F86" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G86">
         <v>3.424072447896261</v>
@@ -4843,22 +4142,22 @@
     </row>
     <row r="87" spans="1:13">
       <c r="A87" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B87">
         <v>10</v>
       </c>
       <c r="C87" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="D87" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="E87">
         <v>8</v>
       </c>
       <c r="F87" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G87">
         <v>0.1449000309115753</v>
@@ -4884,22 +4183,22 @@
     </row>
     <row r="88" spans="1:13">
       <c r="A88" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B88">
         <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="D88" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="E88">
         <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G88">
         <v>-0.4679878857217386</v>
@@ -4925,22 +4224,22 @@
     </row>
     <row r="89" spans="1:13">
       <c r="A89" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B89">
         <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="D89" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="E89">
         <v>8</v>
       </c>
       <c r="F89" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G89">
         <v>-0.4824211510085377</v>
@@ -4966,22 +4265,22 @@
     </row>
     <row r="90" spans="1:13">
       <c r="A90" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B90">
         <v>10</v>
       </c>
       <c r="C90" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="D90" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="E90">
         <v>8</v>
       </c>
       <c r="F90" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G90">
         <v>-0.6128879166333139</v>
@@ -5007,22 +4306,22 @@
     </row>
     <row r="91" spans="1:13">
       <c r="A91" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B91">
         <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="D91" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="E91">
         <v>8</v>
       </c>
       <c r="F91" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G91">
         <v>-0.01443326528680089</v>
@@ -5048,22 +4347,22 @@
     </row>
     <row r="92" spans="1:13">
       <c r="A92" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D92" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E92">
         <v>45</v>
       </c>
       <c r="F92" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G92">
         <v>-0.391823372554704</v>
@@ -5089,22 +4388,22 @@
     </row>
     <row r="93" spans="1:13">
       <c r="A93" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D93" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E93">
         <v>45</v>
       </c>
       <c r="F93" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G93">
         <v>-0.1940848941590687</v>
@@ -5130,22 +4429,22 @@
     </row>
     <row r="94" spans="1:13">
       <c r="A94" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D94" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E94">
         <v>45</v>
       </c>
       <c r="F94" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G94">
         <v>0.8056708833118549</v>
@@ -5171,22 +4470,22 @@
     </row>
     <row r="95" spans="1:13">
       <c r="A95" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D95" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E95">
         <v>45</v>
       </c>
       <c r="F95" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G95">
         <v>0.2659892957331103</v>
@@ -5212,22 +4511,22 @@
     </row>
     <row r="96" spans="1:13">
       <c r="A96" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D96" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E96">
         <v>45</v>
       </c>
       <c r="F96" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G96">
         <v>-0.287973726421626</v>
@@ -5253,22 +4552,22 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D97" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E97">
         <v>45</v>
       </c>
       <c r="F97" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G97">
         <v>-0.4857122048172613</v>
@@ -5294,22 +4593,22 @@
     </row>
     <row r="98" spans="1:13">
       <c r="A98" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E98">
         <v>45</v>
       </c>
       <c r="F98" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G98">
         <v>0.05396938276148333</v>
@@ -5335,22 +4634,22 @@
     </row>
     <row r="99" spans="1:13">
       <c r="A99" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E99">
         <v>45</v>
       </c>
       <c r="F99" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G99">
         <v>-0.1977384783956353</v>
@@ -5376,22 +4675,22 @@
     </row>
     <row r="100" spans="1:13">
       <c r="A100" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D100" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E100">
         <v>45</v>
       </c>
       <c r="F100" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G100">
         <v>0.5396815875787446</v>
@@ -5417,22 +4716,22 @@
     </row>
     <row r="101" spans="1:13">
       <c r="A101" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B101">
         <v>2</v>
       </c>
       <c r="C101" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="D101" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="E101">
         <v>48</v>
       </c>
       <c r="F101" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G101">
         <v>-0.3249025761430264</v>
@@ -5458,22 +4757,22 @@
     </row>
     <row r="102" spans="1:13">
       <c r="A102" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B102">
         <v>2</v>
       </c>
       <c r="C102" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="D102" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="E102">
         <v>48</v>
       </c>
       <c r="F102" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G102">
         <v>-0.02371706183326694</v>
@@ -5499,22 +4798,22 @@
     </row>
     <row r="103" spans="1:13">
       <c r="A103" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B103">
         <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="D103" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="E103">
         <v>48</v>
       </c>
       <c r="F103" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G103">
         <v>1.281557388699246</v>
@@ -5540,22 +4839,22 @@
     </row>
     <row r="104" spans="1:13">
       <c r="A104" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B104">
         <v>2</v>
       </c>
       <c r="C104" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="D104" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="E104">
         <v>48</v>
       </c>
       <c r="F104" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G104">
         <v>0.08471111783642726</v>
@@ -5581,22 +4880,22 @@
     </row>
     <row r="105" spans="1:13">
       <c r="A105" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B105">
         <v>2</v>
       </c>
       <c r="C105" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="D105" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="E105">
         <v>48</v>
       </c>
       <c r="F105" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G105">
         <v>-0.3653535121585669</v>
@@ -5622,22 +4921,22 @@
     </row>
     <row r="106" spans="1:13">
       <c r="A106" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B106">
         <v>2</v>
       </c>
       <c r="C106" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="D106" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="E106">
         <v>48</v>
       </c>
       <c r="F106" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G106">
         <v>-0.6665390264683264</v>
@@ -5663,22 +4962,22 @@
     </row>
     <row r="107" spans="1:13">
       <c r="A107" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="D107" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="E107">
         <v>48</v>
       </c>
       <c r="F107" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G107">
         <v>0.5303072443944927</v>
@@ -5704,22 +5003,22 @@
     </row>
     <row r="108" spans="1:13">
       <c r="A108" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B108">
         <v>2</v>
       </c>
       <c r="C108" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="D108" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="E108">
         <v>48</v>
       </c>
       <c r="F108" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G108">
         <v>-0.3011855143097613</v>
@@ -5745,22 +5044,22 @@
     </row>
     <row r="109" spans="1:13">
       <c r="A109" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="D109" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="E109">
         <v>48</v>
       </c>
       <c r="F109" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G109">
         <v>1.196846270862817</v>
@@ -5786,22 +5085,22 @@
     </row>
     <row r="110" spans="1:13">
       <c r="A110" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B110">
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="D110" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E110">
         <v>48</v>
       </c>
       <c r="F110" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G110">
         <v>-0.004330265375358522</v>
@@ -5827,22 +5126,22 @@
     </row>
     <row r="111" spans="1:13">
       <c r="A111" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B111">
         <v>3</v>
       </c>
       <c r="C111" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="D111" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E111">
         <v>48</v>
       </c>
       <c r="F111" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G111">
         <v>-0.06622332540156961</v>
@@ -5868,22 +5167,22 @@
     </row>
     <row r="112" spans="1:13">
       <c r="A112" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B112">
         <v>3</v>
       </c>
       <c r="C112" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="D112" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E112">
         <v>48</v>
       </c>
       <c r="F112" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G112">
         <v>0.9020729665340852</v>
@@ -5909,22 +5208,22 @@
     </row>
     <row r="113" spans="1:13">
       <c r="A113" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B113">
         <v>3</v>
       </c>
       <c r="C113" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="D113" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E113">
         <v>48</v>
       </c>
       <c r="F113" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G113">
         <v>0.3334282718023722</v>
@@ -5950,22 +5249,22 @@
     </row>
     <row r="114" spans="1:13">
       <c r="A114" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B114">
         <v>3</v>
       </c>
       <c r="C114" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="D114" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E114">
         <v>48</v>
       </c>
       <c r="F114" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G114">
         <v>-0.2442241110438061</v>
@@ -5991,22 +5290,22 @@
     </row>
     <row r="115" spans="1:13">
       <c r="A115" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B115">
         <v>3</v>
       </c>
       <c r="C115" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="D115" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E115">
         <v>48</v>
       </c>
       <c r="F115" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G115">
         <v>-0.1823310510175951</v>
@@ -6032,22 +5331,22 @@
     </row>
     <row r="116" spans="1:13">
       <c r="A116" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B116">
         <v>3</v>
       </c>
       <c r="C116" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="D116" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E116">
         <v>48</v>
       </c>
       <c r="F116" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G116">
         <v>0.3863136437141179</v>
@@ -6073,22 +5372,22 @@
     </row>
     <row r="117" spans="1:13">
       <c r="A117" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B117">
         <v>3</v>
       </c>
       <c r="C117" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="D117" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E117">
         <v>48</v>
       </c>
       <c r="F117" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G117">
         <v>0.06189306002621109</v>
@@ -6114,22 +5413,22 @@
     </row>
     <row r="118" spans="1:13">
       <c r="A118" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B118">
         <v>3</v>
       </c>
       <c r="C118" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="D118" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E118">
         <v>48</v>
       </c>
       <c r="F118" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G118">
         <v>0.568644694731713</v>
@@ -6155,22 +5454,22 @@
     </row>
     <row r="119" spans="1:13">
       <c r="A119" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B119">
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="D119" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="E119">
         <v>16</v>
       </c>
       <c r="F119" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G119">
         <v>0.3800890110219672</v>
@@ -6196,22 +5495,22 @@
     </row>
     <row r="120" spans="1:13">
       <c r="A120" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B120">
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="D120" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="E120">
         <v>16</v>
       </c>
       <c r="F120" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G120">
         <v>0.97462616923975</v>
@@ -6237,22 +5536,22 @@
     </row>
     <row r="121" spans="1:13">
       <c r="A121" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B121">
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="D121" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="E121">
         <v>16</v>
       </c>
       <c r="F121" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G121">
         <v>2.563941585700594</v>
@@ -6278,22 +5577,22 @@
     </row>
     <row r="122" spans="1:13">
       <c r="A122" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B122">
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="D122" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="E122">
         <v>16</v>
       </c>
       <c r="F122" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G122">
         <v>0.009937031033913968</v>
@@ -6319,22 +5618,22 @@
     </row>
     <row r="123" spans="1:13">
       <c r="A123" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B123">
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="D123" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="E123">
         <v>16</v>
       </c>
       <c r="F123" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G123">
         <v>0.01265897952989548</v>
@@ -6360,22 +5659,22 @@
     </row>
     <row r="124" spans="1:13">
       <c r="A124" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B124">
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="D124" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="E124">
         <v>16</v>
       </c>
       <c r="F124" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G124">
         <v>-0.5818781786878873</v>
@@ -6401,22 +5700,22 @@
     </row>
     <row r="125" spans="1:13">
       <c r="A125" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B125">
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="D125" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="E125">
         <v>16</v>
       </c>
       <c r="F125" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G125">
         <v>1.972126375978792</v>
@@ -6442,22 +5741,22 @@
     </row>
     <row r="126" spans="1:13">
       <c r="A126" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B126">
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="D126" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="E126">
         <v>16</v>
       </c>
       <c r="F126" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G126">
         <v>-0.5945371582177827</v>
@@ -6483,22 +5782,22 @@
     </row>
     <row r="127" spans="1:13">
       <c r="A127" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B127">
         <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="D127" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="E127">
         <v>16</v>
       </c>
       <c r="F127" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G127">
         <v>2.55400455466668</v>
@@ -6524,22 +5823,22 @@
     </row>
     <row r="128" spans="1:13">
       <c r="A128" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B128">
         <v>5</v>
       </c>
       <c r="C128" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="D128" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="E128">
         <v>27</v>
       </c>
       <c r="F128" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G128">
         <v>0.3555115673289482</v>
@@ -6565,22 +5864,22 @@
     </row>
     <row r="129" spans="1:13">
       <c r="A129" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B129">
         <v>5</v>
       </c>
       <c r="C129" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="D129" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="E129">
         <v>27</v>
       </c>
       <c r="F129" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G129">
         <v>0.4845314339479927</v>
@@ -6606,22 +5905,22 @@
     </row>
     <row r="130" spans="1:13">
       <c r="A130" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B130">
         <v>5</v>
       </c>
       <c r="C130" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="D130" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="E130">
         <v>27</v>
       </c>
       <c r="F130" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G130">
         <v>1.084166205055331</v>
@@ -6647,22 +5946,22 @@
     </row>
     <row r="131" spans="1:13">
       <c r="A131" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B131">
         <v>5</v>
       </c>
       <c r="C131" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="D131" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="E131">
         <v>27</v>
       </c>
       <c r="F131" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G131">
         <v>-0.453296396289284</v>
@@ -6688,22 +5987,22 @@
     </row>
     <row r="132" spans="1:13">
       <c r="A132" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B132">
         <v>5</v>
       </c>
       <c r="C132" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="D132" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="E132">
         <v>27</v>
       </c>
       <c r="F132" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G132">
         <v>-0.4283231578886539</v>
@@ -6729,22 +6028,22 @@
     </row>
     <row r="133" spans="1:13">
       <c r="A133" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B133">
         <v>5</v>
       </c>
       <c r="C133" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="D133" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="E133">
         <v>27</v>
       </c>
       <c r="F133" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G133">
         <v>-0.5573430245076985</v>
@@ -6770,22 +6069,22 @@
     </row>
     <row r="134" spans="1:13">
       <c r="A134" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B134">
         <v>5</v>
       </c>
       <c r="C134" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="D134" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="E134">
         <v>27</v>
       </c>
       <c r="F134" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G134">
         <v>0.9801195768369162</v>
@@ -6811,22 +6110,22 @@
     </row>
     <row r="135" spans="1:13">
       <c r="A135" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B135">
         <v>5</v>
       </c>
       <c r="C135" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="D135" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="E135">
         <v>27</v>
       </c>
       <c r="F135" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G135">
         <v>-0.1290198666190445</v>
@@ -6852,22 +6151,22 @@
     </row>
     <row r="136" spans="1:13">
       <c r="A136" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B136">
         <v>5</v>
       </c>
       <c r="C136" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="D136" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="E136">
         <v>27</v>
       </c>
       <c r="F136" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G136">
         <v>1.537462601344613</v>
@@ -6893,22 +6192,22 @@
     </row>
     <row r="137" spans="1:13">
       <c r="A137" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B137">
         <v>6</v>
       </c>
       <c r="C137" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D137" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E137">
         <v>48</v>
       </c>
       <c r="F137" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G137">
         <v>-0.5034607715185082</v>
@@ -6934,22 +6233,22 @@
     </row>
     <row r="138" spans="1:13">
       <c r="A138" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B138">
         <v>6</v>
       </c>
       <c r="C138" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D138" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E138">
         <v>48</v>
       </c>
       <c r="F138" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G138">
         <v>-0.1694818644849754</v>
@@ -6975,22 +6274,22 @@
     </row>
     <row r="139" spans="1:13">
       <c r="A139" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B139">
         <v>6</v>
       </c>
       <c r="C139" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D139" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E139">
         <v>48</v>
       </c>
       <c r="F139" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G139">
         <v>0.04843347336528936</v>
@@ -7016,22 +6315,22 @@
     </row>
     <row r="140" spans="1:13">
       <c r="A140" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B140">
         <v>6</v>
       </c>
       <c r="C140" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D140" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E140">
         <v>48</v>
       </c>
       <c r="F140" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G140">
         <v>-0.1970856930885105</v>
@@ -7057,22 +6356,22 @@
     </row>
     <row r="141" spans="1:13">
       <c r="A141" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B141">
         <v>6</v>
       </c>
       <c r="C141" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D141" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E141">
         <v>48</v>
       </c>
       <c r="F141" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G141">
         <v>0.1255715609510943</v>
@@ -7098,22 +6397,22 @@
     </row>
     <row r="142" spans="1:13">
       <c r="A142" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B142">
         <v>6</v>
       </c>
       <c r="C142" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D142" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E142">
         <v>48</v>
       </c>
       <c r="F142" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G142">
         <v>-0.2084073460824385</v>
@@ -7139,22 +6438,22 @@
     </row>
     <row r="143" spans="1:13">
       <c r="A143" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B143">
         <v>6</v>
       </c>
       <c r="C143" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D143" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E143">
         <v>48</v>
       </c>
       <c r="F143" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G143">
         <v>0.0371118203713614</v>
@@ -7180,22 +6479,22 @@
     </row>
     <row r="144" spans="1:13">
       <c r="A144" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B144">
         <v>6</v>
       </c>
       <c r="C144" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D144" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E144">
         <v>48</v>
       </c>
       <c r="F144" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G144">
         <v>-0.3339789070335328</v>
@@ -7221,22 +6520,22 @@
     </row>
     <row r="145" spans="1:13">
       <c r="A145" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B145">
         <v>6</v>
       </c>
       <c r="C145" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D145" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E145">
         <v>48</v>
       </c>
       <c r="F145" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G145">
         <v>0.2455191664537999</v>
@@ -7262,22 +6561,22 @@
     </row>
     <row r="146" spans="1:13">
       <c r="A146" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B146">
         <v>7</v>
       </c>
       <c r="C146" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="D146" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E146">
         <v>48</v>
       </c>
       <c r="F146" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G146">
         <v>0.4892545399312098</v>
@@ -7303,22 +6602,22 @@
     </row>
     <row r="147" spans="1:13">
       <c r="A147" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B147">
         <v>7</v>
       </c>
       <c r="C147" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="D147" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E147">
         <v>48</v>
       </c>
       <c r="F147" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G147">
         <v>0.176617974549373</v>
@@ -7344,22 +6643,22 @@
     </row>
     <row r="148" spans="1:13">
       <c r="A148" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B148">
         <v>7</v>
       </c>
       <c r="C148" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="D148" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E148">
         <v>48</v>
       </c>
       <c r="F148" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G148">
         <v>0.08870720840704038</v>
@@ -7385,22 +6684,22 @@
     </row>
     <row r="149" spans="1:13">
       <c r="A149" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B149">
         <v>7</v>
       </c>
       <c r="C149" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="D149" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E149">
         <v>48</v>
       </c>
       <c r="F149" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G149">
         <v>-0.006477181127575449</v>
@@ -7426,22 +6725,22 @@
     </row>
     <row r="150" spans="1:13">
       <c r="A150" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B150">
         <v>7</v>
       </c>
       <c r="C150" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="D150" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E150">
         <v>48</v>
       </c>
       <c r="F150" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G150">
         <v>-0.1780608567897914</v>
@@ -7467,22 +6766,22 @@
     </row>
     <row r="151" spans="1:13">
       <c r="A151" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B151">
         <v>7</v>
       </c>
       <c r="C151" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="D151" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E151">
         <v>48</v>
       </c>
       <c r="F151" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G151">
         <v>0.1345757085920454</v>
@@ -7508,22 +6807,22 @@
     </row>
     <row r="152" spans="1:13">
       <c r="A152" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B152">
         <v>7</v>
       </c>
       <c r="C152" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="D152" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E152">
         <v>48</v>
       </c>
       <c r="F152" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G152">
         <v>0.2297600981266612</v>
@@ -7549,22 +6848,22 @@
     </row>
     <row r="153" spans="1:13">
       <c r="A153" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B153">
         <v>7</v>
       </c>
       <c r="C153" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="D153" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E153">
         <v>48</v>
       </c>
       <c r="F153" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G153">
         <v>0.3126365653818368</v>
@@ -7590,22 +6889,22 @@
     </row>
     <row r="154" spans="1:13">
       <c r="A154" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B154">
         <v>7</v>
       </c>
       <c r="C154" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="D154" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E154">
         <v>48</v>
       </c>
       <c r="F154" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G154">
         <v>0.09518438953461583</v>
@@ -7631,22 +6930,22 @@
     </row>
     <row r="155" spans="1:13">
       <c r="A155" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B155">
         <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="D155" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E155">
         <v>31</v>
       </c>
       <c r="F155" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G155">
         <v>-0.2619841115590731</v>
@@ -7672,22 +6971,22 @@
     </row>
     <row r="156" spans="1:13">
       <c r="A156" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B156">
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="D156" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E156">
         <v>31</v>
       </c>
       <c r="F156" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G156">
         <v>0.8684029632089221</v>
@@ -7713,22 +7012,22 @@
     </row>
     <row r="157" spans="1:13">
       <c r="A157" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B157">
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="D157" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E157">
         <v>31</v>
       </c>
       <c r="F157" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G157">
         <v>2.277033169352112</v>
@@ -7754,22 +7053,22 @@
     </row>
     <row r="158" spans="1:13">
       <c r="A158" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B158">
         <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="D158" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E158">
         <v>31</v>
       </c>
       <c r="F158" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G158">
         <v>-0.5507751755176606</v>
@@ -7795,22 +7094,22 @@
     </row>
     <row r="159" spans="1:13">
       <c r="A159" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B159">
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="D159" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E159">
         <v>31</v>
       </c>
       <c r="F159" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G159">
         <v>-0.1482318534353588</v>
@@ -7836,22 +7135,22 @@
     </row>
     <row r="160" spans="1:13">
       <c r="A160" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B160">
         <v>8</v>
       </c>
       <c r="C160" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="D160" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E160">
         <v>31</v>
       </c>
       <c r="F160" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G160">
         <v>-1.278618928203354</v>
@@ -7877,22 +7176,22 @@
     </row>
     <row r="161" spans="1:13">
       <c r="A161" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B161">
         <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="D161" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E161">
         <v>31</v>
       </c>
       <c r="F161" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G161">
         <v>1.549189416666419</v>
@@ -7918,22 +7217,22 @@
     </row>
     <row r="162" spans="1:13">
       <c r="A162" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B162">
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="D162" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E162">
         <v>31</v>
       </c>
       <c r="F162" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G162">
         <v>-1.130387074767995</v>
@@ -7959,22 +7258,22 @@
     </row>
     <row r="163" spans="1:13">
       <c r="A163" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B163">
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="D163" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E163">
         <v>31</v>
       </c>
       <c r="F163" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G163">
         <v>2.827808344869773</v>
@@ -8000,22 +7299,22 @@
     </row>
     <row r="164" spans="1:13">
       <c r="A164" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B164">
         <v>9</v>
       </c>
       <c r="C164" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="D164" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E164">
         <v>48</v>
       </c>
       <c r="F164" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G164">
         <v>0.4925335721618929</v>
@@ -8041,22 +7340,22 @@
     </row>
     <row r="165" spans="1:13">
       <c r="A165" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B165">
         <v>9</v>
       </c>
       <c r="C165" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="D165" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E165">
         <v>48</v>
       </c>
       <c r="F165" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G165">
         <v>0.1536900635409388</v>
@@ -8082,22 +7381,22 @@
     </row>
     <row r="166" spans="1:13">
       <c r="A166" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B166">
         <v>9</v>
       </c>
       <c r="C166" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="D166" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E166">
         <v>48</v>
       </c>
       <c r="F166" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G166">
         <v>0.07791532027690806</v>
@@ -8123,22 +7422,22 @@
     </row>
     <row r="167" spans="1:13">
       <c r="A167" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B167">
         <v>9</v>
       </c>
       <c r="C167" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="D167" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E167">
         <v>48</v>
       </c>
       <c r="F167" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G167">
         <v>-0.1052198565555926</v>
@@ -8164,22 +7463,22 @@
     </row>
     <row r="168" spans="1:13">
       <c r="A168" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B168">
         <v>9</v>
       </c>
       <c r="C168" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="D168" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E168">
         <v>48</v>
       </c>
       <c r="F168" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G168">
         <v>-0.268209657646949</v>
@@ -8205,22 +7504,22 @@
     </row>
     <row r="169" spans="1:13">
       <c r="A169" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B169">
         <v>9</v>
       </c>
       <c r="C169" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="D169" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E169">
         <v>48</v>
       </c>
       <c r="F169" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G169">
         <v>0.07063385097400499</v>
@@ -8246,22 +7545,22 @@
     </row>
     <row r="170" spans="1:13">
       <c r="A170" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B170">
         <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="D170" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E170">
         <v>48</v>
       </c>
       <c r="F170" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G170">
         <v>0.2537690278065057</v>
@@ -8287,22 +7586,22 @@
     </row>
     <row r="171" spans="1:13">
       <c r="A171" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B171">
         <v>9</v>
       </c>
       <c r="C171" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="D171" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E171">
         <v>48</v>
       </c>
       <c r="F171" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G171">
         <v>0.338843508620954</v>
@@ -8328,22 +7627,22 @@
     </row>
     <row r="172" spans="1:13">
       <c r="A172" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B172">
         <v>9</v>
       </c>
       <c r="C172" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="D172" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="E172">
         <v>48</v>
       </c>
       <c r="F172" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G172">
         <v>0.1831351768325007</v>
@@ -8369,22 +7668,22 @@
     </row>
     <row r="173" spans="1:13">
       <c r="A173" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B173">
         <v>10</v>
       </c>
       <c r="C173" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D173" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E173">
         <v>9</v>
       </c>
       <c r="F173" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G173">
         <v>0.07669356910266956</v>
@@ -8410,22 +7709,22 @@
     </row>
     <row r="174" spans="1:13">
       <c r="A174" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B174">
         <v>10</v>
       </c>
       <c r="C174" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D174" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E174">
         <v>9</v>
       </c>
       <c r="F174" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G174">
         <v>-0.2764585834661233</v>
@@ -8451,22 +7750,22 @@
     </row>
     <row r="175" spans="1:13">
       <c r="A175" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B175">
         <v>10</v>
       </c>
       <c r="C175" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D175" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E175">
         <v>9</v>
       </c>
       <c r="F175" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G175">
         <v>2.482507761890023</v>
@@ -8492,22 +7791,22 @@
     </row>
     <row r="176" spans="1:13">
       <c r="A176" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B176">
         <v>10</v>
       </c>
       <c r="C176" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D176" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E176">
         <v>9</v>
       </c>
       <c r="F176" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G176">
         <v>0.3396310185709783</v>
@@ -8533,22 +7832,22 @@
     </row>
     <row r="177" spans="1:13">
       <c r="A177" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B177">
         <v>10</v>
       </c>
       <c r="C177" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D177" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E177">
         <v>9</v>
       </c>
       <c r="F177" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G177">
         <v>-0.3048643694495841</v>
@@ -8574,22 +7873,22 @@
     </row>
     <row r="178" spans="1:13">
       <c r="A178" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B178">
         <v>10</v>
       </c>
       <c r="C178" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D178" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E178">
         <v>9</v>
       </c>
       <c r="F178" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G178">
         <v>0.04828778311920878</v>
@@ -8615,22 +7914,22 @@
     </row>
     <row r="179" spans="1:13">
       <c r="A179" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B179">
         <v>10</v>
       </c>
       <c r="C179" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D179" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E179">
         <v>9</v>
       </c>
       <c r="F179" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G179">
         <v>2.191164526438254</v>
@@ -8656,22 +7955,22 @@
     </row>
     <row r="180" spans="1:13">
       <c r="A180" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B180">
         <v>10</v>
       </c>
       <c r="C180" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D180" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E180">
         <v>9</v>
       </c>
       <c r="F180" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G180">
         <v>0.3531521525687928</v>
@@ -8697,22 +7996,22 @@
     </row>
     <row r="181" spans="1:13">
       <c r="A181" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B181">
         <v>10</v>
       </c>
       <c r="C181" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D181" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="E181">
         <v>9</v>
       </c>
       <c r="F181" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G181">
         <v>2.142876743319047</v>
@@ -8738,22 +8037,22 @@
     </row>
     <row r="182" spans="1:13">
       <c r="A182" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B182">
         <v>1</v>
       </c>
       <c r="C182" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D182" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="E182">
         <v>48</v>
       </c>
       <c r="F182" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G182">
         <v>0.3557250617294301</v>
@@ -8779,22 +8078,22 @@
     </row>
     <row r="183" spans="1:13">
       <c r="A183" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B183">
         <v>1</v>
       </c>
       <c r="C183" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D183" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="E183">
         <v>48</v>
       </c>
       <c r="F183" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G183">
         <v>0.5176012113506765</v>
@@ -8820,22 +8119,22 @@
     </row>
     <row r="184" spans="1:13">
       <c r="A184" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B184">
         <v>1</v>
       </c>
       <c r="C184" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D184" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="E184">
         <v>48</v>
       </c>
       <c r="F184" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G184">
         <v>-0.1613572566634112</v>
@@ -8861,22 +8160,22 @@
     </row>
     <row r="185" spans="1:13">
       <c r="A185" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B185">
         <v>1</v>
       </c>
       <c r="C185" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D185" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="E185">
         <v>48</v>
       </c>
       <c r="F185" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G185">
         <v>-0.2198774342290477</v>
@@ -8902,22 +8201,22 @@
     </row>
     <row r="186" spans="1:13">
       <c r="A186" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B186">
         <v>1</v>
       </c>
       <c r="C186" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D186" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="E186">
         <v>48</v>
       </c>
       <c r="F186" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G186">
         <v>-0.05684816884852495</v>
@@ -8943,22 +8242,22 @@
     </row>
     <row r="187" spans="1:13">
       <c r="A187" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B187">
         <v>1</v>
       </c>
       <c r="C187" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D187" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="E187">
         <v>48</v>
       </c>
       <c r="F187" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G187">
         <v>-0.2187243184697714</v>
@@ -8984,22 +8283,22 @@
     </row>
     <row r="188" spans="1:13">
       <c r="A188" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B188">
         <v>1</v>
       </c>
       <c r="C188" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D188" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="E188">
         <v>48</v>
       </c>
       <c r="F188" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G188">
         <v>-0.1602041409041348</v>
@@ -9025,22 +8324,22 @@
     </row>
     <row r="189" spans="1:13">
       <c r="A189" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B189">
         <v>1</v>
       </c>
       <c r="C189" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D189" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="E189">
         <v>48</v>
       </c>
       <c r="F189" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G189">
         <v>-0.1618761496212464</v>
@@ -9066,22 +8365,22 @@
     </row>
     <row r="190" spans="1:13">
       <c r="A190" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B190">
         <v>1</v>
       </c>
       <c r="C190" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D190" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="E190">
         <v>48</v>
       </c>
       <c r="F190" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G190">
         <v>0.05852017756563654</v>
@@ -9107,22 +8406,22 @@
     </row>
     <row r="191" spans="1:13">
       <c r="A191" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B191">
         <v>2</v>
       </c>
       <c r="C191" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D191" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E191">
         <v>25</v>
       </c>
       <c r="F191" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G191">
         <v>0.3576453486208333</v>
@@ -9148,22 +8447,22 @@
     </row>
     <row r="192" spans="1:13">
       <c r="A192" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B192">
         <v>2</v>
       </c>
       <c r="C192" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D192" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E192">
         <v>25</v>
       </c>
       <c r="F192" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G192">
         <v>1.07307224850093</v>
@@ -9189,22 +8488,22 @@
     </row>
     <row r="193" spans="1:13">
       <c r="A193" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B193">
         <v>2</v>
       </c>
       <c r="C193" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D193" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E193">
         <v>25</v>
       </c>
       <c r="F193" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G193">
         <v>0.171002240052637</v>
@@ -9230,22 +8529,22 @@
     </row>
     <row r="194" spans="1:13">
       <c r="A194" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B194">
         <v>2</v>
       </c>
       <c r="C194" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D194" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E194">
         <v>25</v>
       </c>
       <c r="F194" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G194">
         <v>-0.6287036560331387</v>
@@ -9271,22 +8570,22 @@
     </row>
     <row r="195" spans="1:13">
       <c r="A195" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B195">
         <v>2</v>
       </c>
       <c r="C195" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D195" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E195">
         <v>25</v>
       </c>
       <c r="F195" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G195">
         <v>0.1197027363368655</v>
@@ -9312,22 +8611,22 @@
     </row>
     <row r="196" spans="1:13">
       <c r="A196" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B196">
         <v>2</v>
       </c>
       <c r="C196" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D196" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E196">
         <v>25</v>
       </c>
       <c r="F196" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G196">
         <v>-0.5957241635432311</v>
@@ -9353,22 +8652,22 @@
     </row>
     <row r="197" spans="1:13">
       <c r="A197" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B197">
         <v>2</v>
       </c>
       <c r="C197" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D197" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E197">
         <v>25</v>
       </c>
       <c r="F197" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G197">
         <v>0.2039817325425446</v>
@@ -9394,22 +8693,22 @@
     </row>
     <row r="198" spans="1:13">
       <c r="A198" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B198">
         <v>2</v>
       </c>
       <c r="C198" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D198" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E198">
         <v>25</v>
       </c>
       <c r="F198" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G198">
         <v>-0.7154268998800966</v>
@@ -9435,22 +8734,22 @@
     </row>
     <row r="199" spans="1:13">
       <c r="A199" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B199">
         <v>2</v>
       </c>
       <c r="C199" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D199" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="E199">
         <v>25</v>
       </c>
       <c r="F199" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G199">
         <v>0.7997058960857757</v>
@@ -9476,22 +8775,22 @@
     </row>
     <row r="200" spans="1:13">
       <c r="A200" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B200">
         <v>3</v>
       </c>
       <c r="C200" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="D200" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="E200">
         <v>30</v>
       </c>
       <c r="F200" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G200">
         <v>0.5170216148648148</v>
@@ -9517,22 +8816,22 @@
     </row>
     <row r="201" spans="1:13">
       <c r="A201" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B201">
         <v>3</v>
       </c>
       <c r="C201" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="D201" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="E201">
         <v>30</v>
       </c>
       <c r="F201" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G201">
         <v>0.67540205798716</v>
@@ -9558,22 +8857,22 @@
     </row>
     <row r="202" spans="1:13">
       <c r="A202" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B202">
         <v>3</v>
       </c>
       <c r="C202" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="D202" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="E202">
         <v>30</v>
       </c>
       <c r="F202" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G202">
         <v>-0.2488317213011051</v>
@@ -9599,22 +8898,22 @@
     </row>
     <row r="203" spans="1:13">
       <c r="A203" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B203">
         <v>3</v>
       </c>
       <c r="C203" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="D203" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="E203">
         <v>30</v>
       </c>
       <c r="F203" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G203">
         <v>-1.171953920637495</v>
@@ -9640,22 +8939,22 @@
     </row>
     <row r="204" spans="1:13">
       <c r="A204" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B204">
         <v>3</v>
       </c>
       <c r="C204" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="D204" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="E204">
         <v>30</v>
       </c>
       <c r="F204" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G204">
         <v>-0.3431293048765962</v>
@@ -9681,22 +8980,22 @@
     </row>
     <row r="205" spans="1:13">
       <c r="A205" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B205">
         <v>3</v>
       </c>
       <c r="C205" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="D205" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="E205">
         <v>30</v>
       </c>
       <c r="F205" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G205">
         <v>-0.5015097479989414</v>
@@ -9722,22 +9021,22 @@
     </row>
     <row r="206" spans="1:13">
       <c r="A206" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B206">
         <v>3</v>
       </c>
       <c r="C206" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="D206" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="E206">
         <v>30</v>
       </c>
       <c r="F206" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G206">
         <v>0.4216124513374488</v>
@@ -9763,22 +9062,22 @@
     </row>
     <row r="207" spans="1:13">
       <c r="A207" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B207">
         <v>3</v>
       </c>
       <c r="C207" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="D207" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="E207">
         <v>30</v>
       </c>
       <c r="F207" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G207">
         <v>-0.158380443122347</v>
@@ -9804,22 +9103,22 @@
     </row>
     <row r="208" spans="1:13">
       <c r="A208" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B208">
         <v>3</v>
       </c>
       <c r="C208" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="D208" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="E208">
         <v>30</v>
       </c>
       <c r="F208" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G208">
         <v>0.9231221993363903</v>
@@ -9845,22 +9144,22 @@
     </row>
     <row r="209" spans="1:13">
       <c r="A209" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B209">
         <v>4</v>
       </c>
       <c r="C209" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="D209" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="E209">
         <v>47</v>
       </c>
       <c r="F209" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G209">
         <v>0.4976260842770337</v>
@@ -9886,22 +9185,22 @@
     </row>
     <row r="210" spans="1:13">
       <c r="A210" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B210">
         <v>4</v>
       </c>
       <c r="C210" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="D210" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="E210">
         <v>47</v>
       </c>
       <c r="F210" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G210">
         <v>0.9636158105097117</v>
@@ -9927,22 +9226,22 @@
     </row>
     <row r="211" spans="1:13">
       <c r="A211" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B211">
         <v>4</v>
       </c>
       <c r="C211" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="D211" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="E211">
         <v>47</v>
       </c>
       <c r="F211" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G211">
         <v>-0.2542001940096448</v>
@@ -9968,22 +9267,22 @@
     </row>
     <row r="212" spans="1:13">
       <c r="A212" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B212">
         <v>4</v>
       </c>
       <c r="C212" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="D212" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="E212">
         <v>47</v>
       </c>
       <c r="F212" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G212">
         <v>-0.2649800699256666</v>
@@ -10009,22 +9308,22 @@
     </row>
     <row r="213" spans="1:13">
       <c r="A213" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B213">
         <v>4</v>
       </c>
       <c r="C213" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="D213" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="E213">
         <v>47</v>
       </c>
       <c r="F213" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G213">
         <v>-0.09639494389613645</v>
@@ -10050,22 +9349,22 @@
     </row>
     <row r="214" spans="1:13">
       <c r="A214" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B214">
         <v>4</v>
       </c>
       <c r="C214" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="D214" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="E214">
         <v>47</v>
       </c>
       <c r="F214" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G214">
         <v>-0.5623846701288144</v>
@@ -10091,22 +9390,22 @@
     </row>
     <row r="215" spans="1:13">
       <c r="A215" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B215">
         <v>4</v>
       </c>
       <c r="C215" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="D215" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="E215">
         <v>47</v>
       </c>
       <c r="F215" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G215">
         <v>-0.5516047942127926</v>
@@ -10132,22 +9431,22 @@
     </row>
     <row r="216" spans="1:13">
       <c r="A216" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B216">
         <v>4</v>
       </c>
       <c r="C216" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="D216" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="E216">
         <v>47</v>
       </c>
       <c r="F216" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G216">
         <v>-0.465989726232678</v>
@@ -10173,22 +9472,22 @@
     </row>
     <row r="217" spans="1:13">
       <c r="A217" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B217">
         <v>4</v>
       </c>
       <c r="C217" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="D217" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="E217">
         <v>47</v>
       </c>
       <c r="F217" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G217">
         <v>0.01077987591602181</v>
@@ -10214,22 +9513,22 @@
     </row>
     <row r="218" spans="1:13">
       <c r="A218" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B218">
         <v>5</v>
       </c>
       <c r="C218" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="D218" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="E218">
         <v>46</v>
       </c>
       <c r="F218" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G218">
         <v>0.1985065458879873</v>
@@ -10255,22 +9554,22 @@
     </row>
     <row r="219" spans="1:13">
       <c r="A219" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B219">
         <v>5</v>
       </c>
       <c r="C219" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="D219" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="E219">
         <v>46</v>
       </c>
       <c r="F219" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G219">
         <v>0.6861024240967595</v>
@@ -10296,22 +9595,22 @@
     </row>
     <row r="220" spans="1:13">
       <c r="A220" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B220">
         <v>5</v>
       </c>
       <c r="C220" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="D220" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="E220">
         <v>46</v>
       </c>
       <c r="F220" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G220">
         <v>0.2244360034379014</v>
@@ -10337,22 +9636,22 @@
     </row>
     <row r="221" spans="1:13">
       <c r="A221" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B221">
         <v>5</v>
       </c>
       <c r="C221" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="D221" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="E221">
         <v>46</v>
       </c>
       <c r="F221" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G221">
         <v>-0.08500921823731744</v>
@@ -10378,22 +9677,22 @@
     </row>
     <row r="222" spans="1:13">
       <c r="A222" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B222">
         <v>5</v>
       </c>
       <c r="C222" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="D222" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="E222">
         <v>46</v>
       </c>
       <c r="F222" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G222">
         <v>-0.07685714099571328</v>
@@ -10419,22 +9718,22 @@
     </row>
     <row r="223" spans="1:13">
       <c r="A223" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B223">
         <v>5</v>
       </c>
       <c r="C223" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="D223" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="E223">
         <v>46</v>
       </c>
       <c r="F223" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G223">
         <v>-0.5644530192044854</v>
@@ -10460,22 +9759,22 @@
     </row>
     <row r="224" spans="1:13">
       <c r="A224" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B224">
         <v>5</v>
       </c>
       <c r="C224" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="D224" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="E224">
         <v>46</v>
       </c>
       <c r="F224" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G224">
         <v>-0.2550077975292666</v>
@@ -10501,22 +9800,22 @@
     </row>
     <row r="225" spans="1:13">
       <c r="A225" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B225">
         <v>5</v>
       </c>
       <c r="C225" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="D225" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="E225">
         <v>46</v>
       </c>
       <c r="F225" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G225">
         <v>-0.4875958782087721</v>
@@ -10542,22 +9841,22 @@
     </row>
     <row r="226" spans="1:13">
       <c r="A226" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B226">
         <v>5</v>
       </c>
       <c r="C226" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="D226" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="E226">
         <v>46</v>
       </c>
       <c r="F226" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G226">
         <v>0.3094452216752188</v>
@@ -10583,22 +9882,22 @@
     </row>
     <row r="227" spans="1:13">
       <c r="A227" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B227">
         <v>6</v>
       </c>
       <c r="C227" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="D227" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="E227">
         <v>48</v>
       </c>
       <c r="F227" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G227">
         <v>-0.2394666813447301</v>
@@ -10624,22 +9923,22 @@
     </row>
     <row r="228" spans="1:13">
       <c r="A228" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B228">
         <v>6</v>
       </c>
       <c r="C228" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="D228" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="E228">
         <v>48</v>
       </c>
       <c r="F228" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G228">
         <v>0.4417351133790746</v>
@@ -10665,22 +9964,22 @@
     </row>
     <row r="229" spans="1:13">
       <c r="A229" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B229">
         <v>6</v>
       </c>
       <c r="C229" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="D229" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="E229">
         <v>48</v>
       </c>
       <c r="F229" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G229">
         <v>-0.1227554855984572</v>
@@ -10706,22 +10005,22 @@
     </row>
     <row r="230" spans="1:13">
       <c r="A230" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B230">
         <v>6</v>
       </c>
       <c r="C230" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="D230" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="E230">
         <v>48</v>
       </c>
       <c r="F230" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G230">
         <v>-1.084156289581664</v>
@@ -10747,22 +10046,22 @@
     </row>
     <row r="231" spans="1:13">
       <c r="A231" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B231">
         <v>6</v>
       </c>
       <c r="C231" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="D231" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="E231">
         <v>48</v>
       </c>
       <c r="F231" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G231">
         <v>0.2563888355887087</v>
@@ -10788,22 +10087,22 @@
     </row>
     <row r="232" spans="1:13">
       <c r="A232" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B232">
         <v>6</v>
       </c>
       <c r="C232" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="D232" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="E232">
         <v>48</v>
       </c>
       <c r="F232" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G232">
         <v>-0.424812959135096</v>
@@ -10829,22 +10128,22 @@
     </row>
     <row r="233" spans="1:13">
       <c r="A233" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B233">
         <v>6</v>
       </c>
       <c r="C233" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="D233" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="E233">
         <v>48</v>
       </c>
       <c r="F233" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G233">
         <v>0.5365878448481105</v>
@@ -10870,22 +10169,22 @@
     </row>
     <row r="234" spans="1:13">
       <c r="A234" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B234">
         <v>6</v>
       </c>
       <c r="C234" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="D234" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="E234">
         <v>48</v>
       </c>
       <c r="F234" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G234">
         <v>-0.6812017947238047</v>
@@ -10911,22 +10210,22 @@
     </row>
     <row r="235" spans="1:13">
       <c r="A235" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B235">
         <v>6</v>
       </c>
       <c r="C235" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="D235" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="E235">
         <v>48</v>
       </c>
       <c r="F235" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G235">
         <v>0.9614008039832065</v>
@@ -10952,22 +10251,22 @@
     </row>
     <row r="236" spans="1:13">
       <c r="A236" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B236">
         <v>7</v>
       </c>
       <c r="C236" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D236" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="E236">
         <v>20</v>
       </c>
       <c r="F236" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G236">
         <v>0.4663525406741069</v>
@@ -10993,22 +10292,22 @@
     </row>
     <row r="237" spans="1:13">
       <c r="A237" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B237">
         <v>7</v>
       </c>
       <c r="C237" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D237" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="E237">
         <v>20</v>
       </c>
       <c r="F237" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G237">
         <v>1.093068353190146</v>
@@ -11034,22 +10333,22 @@
     </row>
     <row r="238" spans="1:13">
       <c r="A238" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B238">
         <v>7</v>
       </c>
       <c r="C238" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D238" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="E238">
         <v>20</v>
       </c>
       <c r="F238" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G238">
         <v>-0.2732519537734301</v>
@@ -11075,22 +10374,22 @@
     </row>
     <row r="239" spans="1:13">
       <c r="A239" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B239">
         <v>7</v>
       </c>
       <c r="C239" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D239" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="E239">
         <v>20</v>
       </c>
       <c r="F239" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G239">
         <v>-1.300743213318333</v>
@@ -11116,22 +10415,22 @@
     </row>
     <row r="240" spans="1:13">
       <c r="A240" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B240">
         <v>7</v>
       </c>
       <c r="C240" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D240" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="E240">
         <v>20</v>
       </c>
       <c r="F240" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G240">
         <v>-0.05544032409114052</v>
@@ -11157,22 +10456,22 @@
     </row>
     <row r="241" spans="1:13">
       <c r="A241" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B241">
         <v>7</v>
       </c>
       <c r="C241" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D241" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="E241">
         <v>20</v>
       </c>
       <c r="F241" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G241">
         <v>-0.6821561366071798</v>
@@ -11198,22 +10497,22 @@
     </row>
     <row r="242" spans="1:13">
       <c r="A242" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B242">
         <v>7</v>
       </c>
       <c r="C242" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D242" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="E242">
         <v>20</v>
       </c>
       <c r="F242" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G242">
         <v>0.3453351229377226</v>
@@ -11239,22 +10538,22 @@
     </row>
     <row r="243" spans="1:13">
       <c r="A243" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B243">
         <v>7</v>
       </c>
       <c r="C243" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D243" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="E243">
         <v>20</v>
       </c>
       <c r="F243" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G243">
         <v>-0.6267158125160393</v>
@@ -11280,22 +10579,22 @@
     </row>
     <row r="244" spans="1:13">
       <c r="A244" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B244">
         <v>7</v>
       </c>
       <c r="C244" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D244" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="E244">
         <v>20</v>
       </c>
       <c r="F244" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G244">
         <v>1.027491259544901</v>
@@ -11321,22 +10620,22 @@
     </row>
     <row r="245" spans="1:13">
       <c r="A245" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B245">
         <v>8</v>
       </c>
       <c r="C245" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D245" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="E245">
         <v>42</v>
       </c>
       <c r="F245" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G245">
         <v>0.5786139368860255</v>
@@ -11362,22 +10661,22 @@
     </row>
     <row r="246" spans="1:13">
       <c r="A246" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B246">
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D246" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="E246">
         <v>42</v>
       </c>
       <c r="F246" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G246">
         <v>1.015091242999762</v>
@@ -11403,22 +10702,22 @@
     </row>
     <row r="247" spans="1:13">
       <c r="A247" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B247">
         <v>8</v>
       </c>
       <c r="C247" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D247" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="E247">
         <v>42</v>
       </c>
       <c r="F247" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G247">
         <v>-0.2275266793368473</v>
@@ -11444,22 +10743,22 @@
     </row>
     <row r="248" spans="1:13">
       <c r="A248" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B248">
         <v>8</v>
       </c>
       <c r="C248" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D248" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="E248">
         <v>42</v>
       </c>
       <c r="F248" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G248">
         <v>-0.2057871665050897</v>
@@ -11485,22 +10784,22 @@
     </row>
     <row r="249" spans="1:13">
       <c r="A249" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B249">
         <v>8</v>
       </c>
       <c r="C249" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D249" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="E249">
         <v>42</v>
       </c>
       <c r="F249" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G249">
         <v>0.1152519061604309</v>
@@ -11526,22 +10825,22 @@
     </row>
     <row r="250" spans="1:13">
       <c r="A250" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B250">
         <v>8</v>
       </c>
       <c r="C250" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D250" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="E250">
         <v>42</v>
       </c>
       <c r="F250" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G250">
         <v>-0.3212253999533061</v>
@@ -11567,22 +10866,22 @@
     </row>
     <row r="251" spans="1:13">
       <c r="A251" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B251">
         <v>8</v>
       </c>
       <c r="C251" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D251" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="E251">
         <v>42</v>
       </c>
       <c r="F251" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G251">
         <v>-0.3429649127850638</v>
@@ -11608,22 +10907,22 @@
     </row>
     <row r="252" spans="1:13">
       <c r="A252" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B252">
         <v>8</v>
       </c>
       <c r="C252" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D252" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="E252">
         <v>42</v>
       </c>
       <c r="F252" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G252">
         <v>-0.436477306113737</v>
@@ -11649,22 +10948,22 @@
     </row>
     <row r="253" spans="1:13">
       <c r="A253" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B253">
         <v>8</v>
       </c>
       <c r="C253" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D253" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="E253">
         <v>42</v>
       </c>
       <c r="F253" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G253">
         <v>-0.02173951283175768</v>
@@ -11690,22 +10989,22 @@
     </row>
     <row r="254" spans="1:13">
       <c r="A254" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B254">
         <v>9</v>
       </c>
       <c r="C254" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="D254" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E254">
         <v>48</v>
       </c>
       <c r="F254" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G254">
         <v>0.2350701150881953</v>
@@ -11731,22 +11030,22 @@
     </row>
     <row r="255" spans="1:13">
       <c r="A255" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B255">
         <v>9</v>
       </c>
       <c r="C255" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="D255" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E255">
         <v>48</v>
       </c>
       <c r="F255" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G255">
         <v>0.4677328517419674</v>
@@ -11772,22 +11071,22 @@
     </row>
     <row r="256" spans="1:13">
       <c r="A256" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B256">
         <v>9</v>
       </c>
       <c r="C256" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="D256" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E256">
         <v>48</v>
       </c>
       <c r="F256" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G256">
         <v>-0.2379029695815298</v>
@@ -11813,22 +11112,22 @@
     </row>
     <row r="257" spans="1:13">
       <c r="A257" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B257">
         <v>9</v>
       </c>
       <c r="C257" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="D257" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E257">
         <v>48</v>
       </c>
       <c r="F257" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G257">
         <v>-0.1459132355237074</v>
@@ -11854,22 +11153,22 @@
     </row>
     <row r="258" spans="1:13">
       <c r="A258" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B258">
         <v>9</v>
       </c>
       <c r="C258" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="D258" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E258">
         <v>48</v>
       </c>
       <c r="F258" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G258">
         <v>0.1240388554337741</v>
@@ -11895,22 +11194,22 @@
     </row>
     <row r="259" spans="1:13">
       <c r="A259" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B259">
         <v>9</v>
       </c>
       <c r="C259" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="D259" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E259">
         <v>48</v>
       </c>
       <c r="F259" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G259">
         <v>-0.108623881219998</v>
@@ -11936,22 +11235,22 @@
     </row>
     <row r="260" spans="1:13">
       <c r="A260" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B260">
         <v>9</v>
       </c>
       <c r="C260" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="D260" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E260">
         <v>48</v>
       </c>
       <c r="F260" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G260">
         <v>-0.2006136152778204</v>
@@ -11977,22 +11276,22 @@
     </row>
     <row r="261" spans="1:13">
       <c r="A261" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B261">
         <v>9</v>
       </c>
       <c r="C261" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="D261" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E261">
         <v>48</v>
       </c>
       <c r="F261" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G261">
         <v>-0.2326627366537721</v>
@@ -12018,22 +11317,22 @@
     </row>
     <row r="262" spans="1:13">
       <c r="A262" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B262">
         <v>9</v>
       </c>
       <c r="C262" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="D262" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E262">
         <v>48</v>
       </c>
       <c r="F262" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G262">
         <v>-0.0919897340578224</v>
@@ -12059,22 +11358,22 @@
     </row>
     <row r="263" spans="1:13">
       <c r="A263" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B263">
         <v>10</v>
       </c>
       <c r="C263" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="D263" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E263">
         <v>48</v>
       </c>
       <c r="F263" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G263">
         <v>0.2140064057394433</v>
@@ -12100,22 +11399,22 @@
     </row>
     <row r="264" spans="1:13">
       <c r="A264" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B264">
         <v>10</v>
       </c>
       <c r="C264" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="D264" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E264">
         <v>48</v>
       </c>
       <c r="F264" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G264">
         <v>0.5142649477887247</v>
@@ -12141,22 +11440,22 @@
     </row>
     <row r="265" spans="1:13">
       <c r="A265" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B265">
         <v>10</v>
       </c>
       <c r="C265" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="D265" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E265">
         <v>48</v>
       </c>
       <c r="F265" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G265">
         <v>-0.07160964398410385</v>
@@ -12182,22 +11481,22 @@
     </row>
     <row r="266" spans="1:13">
       <c r="A266" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B266">
         <v>10</v>
       </c>
       <c r="C266" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="D266" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E266">
         <v>48</v>
       </c>
       <c r="F266" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="G266">
         <v>-0.2285417833280761</v>
@@ -12223,22 +11522,22 @@
     </row>
     <row r="267" spans="1:13">
       <c r="A267" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B267">
         <v>10</v>
       </c>
       <c r="C267" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="D267" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E267">
         <v>48</v>
       </c>
       <c r="F267" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G267">
         <v>0.05697472096795764</v>
@@ -12264,22 +11563,22 @@
     </row>
     <row r="268" spans="1:13">
       <c r="A268" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B268">
         <v>10</v>
       </c>
       <c r="C268" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="D268" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E268">
         <v>48</v>
       </c>
       <c r="F268" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="G268">
         <v>-0.2432838210813237</v>
@@ -12305,22 +11604,22 @@
     </row>
     <row r="269" spans="1:13">
       <c r="A269" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B269">
         <v>10</v>
       </c>
       <c r="C269" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="D269" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E269">
         <v>48</v>
       </c>
       <c r="F269" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G269">
         <v>-0.08635168173735153</v>
@@ -12346,22 +11645,22 @@
     </row>
     <row r="270" spans="1:13">
       <c r="A270" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B270">
         <v>10</v>
       </c>
       <c r="C270" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="D270" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E270">
         <v>48</v>
       </c>
       <c r="F270" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G270">
         <v>-0.3002585420492814</v>
@@ -12387,22 +11686,22 @@
     </row>
     <row r="271" spans="1:13">
       <c r="A271" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="B271">
         <v>10</v>
       </c>
       <c r="C271" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="D271" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E271">
         <v>48</v>
       </c>
       <c r="F271" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="G271">
         <v>0.1569321393439722</v>
@@ -12424,598 +11723,6 @@
       </c>
       <c r="M271">
         <v>0.0008944009341007776</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B10" t="s">
-        <v>143</v>
-      </c>
-      <c r="C10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B11" t="s">
-        <v>145</v>
-      </c>
-      <c r="C11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>146</v>
-      </c>
-      <c r="B12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>148</v>
-      </c>
-      <c r="B13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C13" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>150</v>
-      </c>
-      <c r="B14" t="s">
-        <v>151</v>
-      </c>
-      <c r="C14" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B15" t="s">
-        <v>154</v>
-      </c>
-      <c r="C15" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>155</v>
-      </c>
-      <c r="B16" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B17" t="s">
-        <v>158</v>
-      </c>
-      <c r="C17" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>159</v>
-      </c>
-      <c r="B18" t="s">
-        <v>160</v>
-      </c>
-      <c r="C18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>161</v>
-      </c>
-      <c r="B19" t="s">
-        <v>162</v>
-      </c>
-      <c r="C19" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>163</v>
-      </c>
-      <c r="B20" t="s">
-        <v>164</v>
-      </c>
-      <c r="C20" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>165</v>
-      </c>
-      <c r="B21" t="s">
-        <v>166</v>
-      </c>
-      <c r="C21" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>167</v>
-      </c>
-      <c r="B22" t="s">
-        <v>168</v>
-      </c>
-      <c r="C22" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>169</v>
-      </c>
-      <c r="B23" t="s">
-        <v>170</v>
-      </c>
-      <c r="C23" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>171</v>
-      </c>
-      <c r="B24" t="s">
-        <v>172</v>
-      </c>
-      <c r="C24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>173</v>
-      </c>
-      <c r="B25" t="s">
-        <v>174</v>
-      </c>
-      <c r="C25" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>175</v>
-      </c>
-      <c r="B26" t="s">
-        <v>176</v>
-      </c>
-      <c r="C26" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>177</v>
-      </c>
-      <c r="B27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C27" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>179</v>
-      </c>
-      <c r="B28" t="s">
-        <v>180</v>
-      </c>
-      <c r="C28" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>181</v>
-      </c>
-      <c r="B29" t="s">
-        <v>182</v>
-      </c>
-      <c r="C29" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>183</v>
-      </c>
-      <c r="B30" t="s">
-        <v>184</v>
-      </c>
-      <c r="C30" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>185</v>
-      </c>
-      <c r="B31" t="s">
-        <v>186</v>
-      </c>
-      <c r="C31" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>187</v>
-      </c>
-      <c r="B32" t="s">
-        <v>188</v>
-      </c>
-      <c r="C32" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>189</v>
-      </c>
-      <c r="B33" t="s">
-        <v>190</v>
-      </c>
-      <c r="C33" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>191</v>
-      </c>
-      <c r="B34" t="s">
-        <v>192</v>
-      </c>
-      <c r="C34" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>193</v>
-      </c>
-      <c r="B35" t="s">
-        <v>194</v>
-      </c>
-      <c r="C35" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>195</v>
-      </c>
-      <c r="B36" t="s">
-        <v>196</v>
-      </c>
-      <c r="C36" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>197</v>
-      </c>
-      <c r="B37" t="s">
-        <v>198</v>
-      </c>
-      <c r="C37" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>199</v>
-      </c>
-      <c r="B38" t="s">
-        <v>200</v>
-      </c>
-      <c r="C38" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>201</v>
-      </c>
-      <c r="B39" t="s">
-        <v>202</v>
-      </c>
-      <c r="C39" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
-        <v>203</v>
-      </c>
-      <c r="B40" t="s">
-        <v>204</v>
-      </c>
-      <c r="C40" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
-        <v>205</v>
-      </c>
-      <c r="B41" t="s">
-        <v>206</v>
-      </c>
-      <c r="C41" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>207</v>
-      </c>
-      <c r="B42" t="s">
-        <v>208</v>
-      </c>
-      <c r="C42" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>209</v>
-      </c>
-      <c r="B43" t="s">
-        <v>141</v>
-      </c>
-      <c r="C43" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
-        <v>210</v>
-      </c>
-      <c r="B44" t="s">
-        <v>211</v>
-      </c>
-      <c r="C44" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>212</v>
-      </c>
-      <c r="B45" t="s">
-        <v>213</v>
-      </c>
-      <c r="C45" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
-        <v>214</v>
-      </c>
-      <c r="B46" t="s">
-        <v>215</v>
-      </c>
-      <c r="C46" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>216</v>
-      </c>
-      <c r="B47" t="s">
-        <v>217</v>
-      </c>
-      <c r="C47" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>218</v>
-      </c>
-      <c r="B48" t="s">
-        <v>219</v>
-      </c>
-      <c r="C48" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
-        <v>220</v>
-      </c>
-      <c r="B49" t="s">
-        <v>221</v>
-      </c>
-      <c r="C49" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
-        <v>222</v>
-      </c>
-      <c r="B50" t="s">
-        <v>223</v>
-      </c>
-      <c r="C50" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
